--- a/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92539650597</v>
+        <v>46157.93113575048</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93113575048</v>
+        <v>46157.93368037255</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93368037255</v>
+        <v>46157.93671574206</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93671574206</v>
+        <v>46158.28194019948</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28194019948</v>
+        <v>46158.29717777314</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29717777314</v>
+        <v>46158.29790065555</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29790065555</v>
+        <v>46158.33355622069</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33355622069</v>
+        <v>46158.37210581473</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/16. ООО Каффа (автозапчасти)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37210581473</v>
+        <v>46158.37267594587</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
